--- a/Local/faqs.xlsx
+++ b/Local/faqs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\Tesis\Local\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09906CF-F33C-448F-AEEE-76FF422916E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8454752F-BE5C-4E20-845A-1188B4D5C8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>type</t>
   </si>
@@ -353,18 +353,34 @@
       <t>. 🏞️🔥</t>
     </r>
   </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>¿Cuál es el proceso de inscripción de la Rio21k?</t>
+  </si>
+  <si>
+    <t>imagenes\inscripcion_rio21k.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -425,16 +441,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.21875" style="1" customWidth="1"/>
@@ -927,6 +946,17 @@
         <v>47</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Local/faqs.xlsx
+++ b/Local/faqs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F155187F-F99D-4514-BC98-C128769968B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{232E398A-C589-4222-B07B-53C22CBBA64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{33AE59F7-EEA7-440D-A318-637E5ABD064C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{33AE59F7-EEA7-440D-A318-637E5ABD064C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="194">
   <si>
     <t>type</t>
   </si>
@@ -746,6 +746,100 @@
   </si>
   <si>
     <t>faq</t>
+  </si>
+  <si>
+    <t>Cuáles son las categorías de la Ruta del Hielero</t>
+  </si>
+  <si>
+    <t>Cuáles son las categorías</t>
+  </si>
+  <si>
+    <t>Para indicarte las categorías, coméntame de qué carrera quisieras saber?</t>
+  </si>
+  <si>
+    <t>Cuáles son las categorías del Altar Reto Trail</t>
+  </si>
+  <si>
+    <t>Cuáles son las categorías de la Rio 21K</t>
+  </si>
+  <si>
+    <t>5K
+* Infantil hasta 12 años
+* Juvenil 13 a 18 años
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50 a 59 años
+* Super Máster 60+ años
+10K
+* Juvenil hasta los 18 años
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50+ años
+* Super Máster 60+ años
+25K - 40K - 70K
+* Abierta hasta los 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50+ años</t>
+  </si>
+  <si>
+    <t>5K
+* Infantil hasta 12 años
+* Juvenil 13 a 18 años
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50 a 59 años
+* Super Máster 60+ años
+10K
+* Juvenil hasta los 18 años
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50+ años
+* Super Máster 60+ años
+25K - 40K - 70K
+* Abierta hasta los 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50+ años
+7K
+Infantil hasta 12 años
+Juvenil 13 a 18 años
+Abierta 19 a 29 años
+Máster A 30 a 39 años
+Máster B 40 a 49 años
+Máster C 50 a 59 años
+Súper Máster 60+ años
+3.5 - 5.5K
+Abierta hasta los 29 años
+Máster A 30 a 39 años
+Máster B 40 a 49 años
+Máster C 50 a 59 años</t>
+  </si>
+  <si>
+    <t>21K
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50 a 59 años
+* Super Máster 60 en adelante
+10K
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50 a 59 años
+* Super Máster 60 en adelante
+5K
+* Infantil hasta 13 años
+* Juvenil 14 a 18 años
+* Abierta 19 a 29 años
+* Máster A 30 a 39 años
+* Máster B 40 a 49 años
+* Máster C 50 a 59 años
+* Super Máster 60 en adelante</t>
   </si>
 </sst>
 </file>
@@ -849,7 +943,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -868,6 +962,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1204,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C282893E-7595-4F10-A40A-905CC2B16B30}">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="50" style="2" customWidth="1"/>
@@ -1299,70 +1399,70 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="360" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="360" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row r="14" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>185</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -1370,7 +1470,7 @@
         <v>185</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1381,7 +1481,7 @@
         <v>185</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>30</v>
@@ -1392,7 +1492,7 @@
         <v>185</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>30</v>
@@ -1403,7 +1503,7 @@
         <v>185</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>30</v>
@@ -1414,7 +1514,7 @@
         <v>185</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>30</v>
@@ -1425,65 +1525,65 @@
         <v>185</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>185</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>185</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>185</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
@@ -1491,7 +1591,7 @@
         <v>185</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>47</v>
@@ -1502,7 +1602,7 @@
         <v>185</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>47</v>
@@ -1513,7 +1613,7 @@
         <v>185</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>47</v>
@@ -1524,7 +1624,7 @@
         <v>185</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>47</v>
@@ -1535,7 +1635,7 @@
         <v>185</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>47</v>
@@ -1546,7 +1646,7 @@
         <v>185</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>47</v>
@@ -1557,7 +1657,7 @@
         <v>185</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>47</v>
@@ -1567,8 +1667,8 @@
       <c r="A33" t="s">
         <v>185</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>44</v>
+      <c r="B33" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>47</v>
@@ -1578,8 +1678,8 @@
       <c r="A34" t="s">
         <v>185</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>45</v>
+      <c r="B34" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>47</v>
@@ -1589,55 +1689,55 @@
       <c r="A35" t="s">
         <v>185</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>46</v>
+      <c r="B35" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>185</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>185</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>49</v>
+      <c r="B37" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>185</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>50</v>
+      <c r="B38" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>51</v>
+      <c r="B39" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
@@ -1645,7 +1745,7 @@
         <v>185</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>61</v>
@@ -1656,7 +1756,7 @@
         <v>185</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>61</v>
@@ -1667,7 +1767,7 @@
         <v>185</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>61</v>
@@ -1678,7 +1778,7 @@
         <v>185</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>61</v>
@@ -1689,7 +1789,7 @@
         <v>185</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>61</v>
@@ -1700,7 +1800,7 @@
         <v>185</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>61</v>
@@ -1711,7 +1811,7 @@
         <v>185</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>61</v>
@@ -1722,7 +1822,7 @@
         <v>185</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>61</v>
@@ -1733,54 +1833,54 @@
         <v>185</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>185</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>185</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>185</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>185</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
@@ -1788,7 +1888,7 @@
         <v>185</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>72</v>
@@ -1799,7 +1899,7 @@
         <v>185</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>72</v>
@@ -1810,7 +1910,7 @@
         <v>185</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>72</v>
@@ -1821,7 +1921,7 @@
         <v>185</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>72</v>
@@ -1832,7 +1932,7 @@
         <v>185</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>72</v>
@@ -1843,7 +1943,7 @@
         <v>185</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>72</v>
@@ -1854,54 +1954,54 @@
         <v>185</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>185</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>185</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>185</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>185</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -1909,7 +2009,7 @@
         <v>185</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>82</v>
@@ -1920,7 +2020,7 @@
         <v>185</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>82</v>
@@ -1931,7 +2031,7 @@
         <v>185</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>82</v>
@@ -1942,7 +2042,7 @@
         <v>185</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>82</v>
@@ -1953,54 +2053,54 @@
         <v>185</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>185</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>185</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>185</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>185</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -2008,7 +2108,7 @@
         <v>185</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>92</v>
@@ -2019,7 +2119,7 @@
         <v>185</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>92</v>
@@ -2030,7 +2130,7 @@
         <v>185</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>92</v>
@@ -2041,7 +2141,7 @@
         <v>185</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>92</v>
@@ -2052,54 +2152,54 @@
         <v>185</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>185</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>185</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>185</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>185</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
@@ -2107,7 +2207,7 @@
         <v>185</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>105</v>
@@ -2118,7 +2218,7 @@
         <v>185</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>105</v>
@@ -2129,7 +2229,7 @@
         <v>185</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>105</v>
@@ -2140,7 +2240,7 @@
         <v>185</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>105</v>
@@ -2151,7 +2251,7 @@
         <v>185</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>105</v>
@@ -2162,7 +2262,7 @@
         <v>185</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>105</v>
@@ -2173,7 +2273,7 @@
         <v>185</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>105</v>
@@ -2184,54 +2284,54 @@
         <v>185</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>185</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>185</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>185</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>185</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -2239,7 +2339,7 @@
         <v>185</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>125</v>
@@ -2250,7 +2350,7 @@
         <v>185</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>125</v>
@@ -2261,7 +2361,7 @@
         <v>185</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>125</v>
@@ -2272,7 +2372,7 @@
         <v>185</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>125</v>
@@ -2283,7 +2383,7 @@
         <v>185</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -2294,7 +2394,7 @@
         <v>185</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>125</v>
@@ -2305,7 +2405,7 @@
         <v>185</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>125</v>
@@ -2316,7 +2416,7 @@
         <v>185</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>125</v>
@@ -2327,7 +2427,7 @@
         <v>185</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>125</v>
@@ -2338,7 +2438,7 @@
         <v>185</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>125</v>
@@ -2349,7 +2449,7 @@
         <v>185</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>125</v>
@@ -2360,7 +2460,7 @@
         <v>185</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -2371,7 +2471,7 @@
         <v>185</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>125</v>
@@ -2382,7 +2482,7 @@
         <v>185</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>125</v>
@@ -2393,54 +2493,54 @@
         <v>185</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>185</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>185</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>185</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>185</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
@@ -2448,7 +2548,7 @@
         <v>185</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>141</v>
@@ -2459,7 +2559,7 @@
         <v>185</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>141</v>
@@ -2470,7 +2570,7 @@
         <v>185</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>141</v>
@@ -2481,7 +2581,7 @@
         <v>185</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>141</v>
@@ -2492,7 +2592,7 @@
         <v>185</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>141</v>
@@ -2503,7 +2603,7 @@
         <v>185</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>141</v>
@@ -2514,7 +2614,7 @@
         <v>185</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>141</v>
@@ -2525,7 +2625,7 @@
         <v>185</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>141</v>
@@ -2536,7 +2636,7 @@
         <v>185</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>141</v>
@@ -2547,7 +2647,7 @@
         <v>185</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>141</v>
@@ -2558,54 +2658,54 @@
         <v>185</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>185</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>185</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>185</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>185</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2613,10 +2713,10 @@
         <v>185</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2624,10 +2724,10 @@
         <v>185</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2635,10 +2735,10 @@
         <v>185</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2646,10 +2746,10 @@
         <v>185</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2657,10 +2757,10 @@
         <v>185</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2668,10 +2768,10 @@
         <v>185</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2679,10 +2779,10 @@
         <v>185</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2690,10 +2790,10 @@
         <v>185</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2701,10 +2801,10 @@
         <v>185</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
@@ -2712,54 +2812,54 @@
         <v>185</v>
       </c>
       <c r="B137" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>185</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>185</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>185</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>185</v>
+      </c>
+      <c r="B141" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C137" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>185</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>185</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>185</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>185</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -2767,10 +2867,10 @@
         <v>185</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -2778,31 +2878,75 @@
         <v>185</v>
       </c>
       <c r="B143" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>185</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>185</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>185</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>185</v>
+      </c>
+      <c r="B147" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C147" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>185</v>
-      </c>
-      <c r="B144" s="4" t="s">
+    <row r="148" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>185</v>
+      </c>
+      <c r="B148" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C148" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>185</v>
-      </c>
-      <c r="B145" s="3" t="s">
+    <row r="149" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>185</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C145" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>184</v>
       </c>
     </row>
